--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/araucania.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2389-710-CM25</t>
+          <t>2548-526-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2537.56</v>
+        <v>9094.959999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1028897-1614-CM25</t>
+          <t>4170-213-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>65.154.272-3</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>28141.83</v>
+        <v>40763.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3836-935-CM25</t>
+          <t>1057780-58-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.191.400-3</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8770.299999999999</v>
+        <v>36168.31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3861-262-CM25</t>
+          <t>2389-710-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.191.400-3</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1594.6</v>
+        <v>2537.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3151-662-CM25</t>
+          <t>1028897-1614-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>65.154.272-3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>18763.96</v>
+        <v>28141.83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1426099-232-CM25</t>
+          <t>3836-935-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.191.400-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE TOLTEN</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9282</v>
+        <v>8770.299999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3200-625-CM25</t>
+          <t>3861-262-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.191.400-3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE TOLTEN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5071.46</v>
+        <v>1594.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3887-602-CM25</t>
+          <t>3151-662-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>46156.53</v>
+        <v>18763.96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3201-450-CM25</t>
+          <t>1426099-232-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Site Chile Sociedad Anónima</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.988.790-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3538.23</v>
+        <v>9282</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3697-180-CM26</t>
+          <t>3200-625-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7096.21</v>
+        <v>5071.46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3486-114-CM26</t>
+          <t>3887-602-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.190.400-8</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>13744.5</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3485-246-CM26</t>
+          <t>3201-450-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.190.400-8</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>13744.5</v>
+        <v>3538.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3495-61-CM26</t>
+          <t>3697-180-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SEIDOR TECHNOLOGIES S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.449.580-2</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>22184.58</v>
+        <v>7096.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>722-27-CM26</t>
+          <t>3486-114-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>69.190.400-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>30742.22</v>
+        <v>13744.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4284-148-CM26</t>
+          <t>3485-246-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>69.190.400-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>48786.43</v>
+        <v>13744.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2548-229-CM26</t>
+          <t>3495-61-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SEIDOR TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.449.580-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9721.82</v>
+        <v>22184.58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3708-146-CM26</t>
+          <t>722-27-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>32092.52</v>
+        <v>30742.22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3517-60-CM26</t>
+          <t>4284-148-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5588.26</v>
+        <v>48786.43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4322-265-CM26</t>
+          <t>2548-229-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4015.54</v>
+        <v>9721.82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4179-622-CM26</t>
+          <t>3708-146-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6424.57</v>
+        <v>32092.52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4322-332-CM26</t>
+          <t>3517-60-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>845.28</v>
+        <v>5588.26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3921-323-CM26</t>
+          <t>4322-265-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>22175.65</v>
+        <v>4015.54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5586-2119-CM26</t>
+          <t>4179-622-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>62229.5</v>
+        <v>6424.57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3517-103-CM26</t>
+          <t>4322-332-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,6 +1972,189 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
+        <v>845.28</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5586-2119-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>87.912.900-1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>62229.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3921-323-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.191.500-K</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>22175.65</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3517-103-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.180.700-2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CLOUDLATAM SPA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
         <v>1774.05</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/araucania.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/araucania.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Araucanía" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Araucanía" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2548-526-CM25</t>
+          <t>2546-56-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9094.959999999999</v>
+        <v>5593</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4170-213-CM25</t>
+          <t>4284-66-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>40763.45</v>
+        <v>48825.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1057780-58-CM25</t>
+          <t>3153-47-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.955.100-1</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>36168.31</v>
+        <v>13044.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2389-710-CM25</t>
+          <t>1180740-6-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2537.56</v>
+        <v>1692.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1028897-1614-CM25</t>
+          <t>3212-52-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.154.272-3</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>28141.83</v>
+        <v>1057.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3836-935-CM25</t>
+          <t>722-35-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.191.400-3</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8770.299999999999</v>
+        <v>30773.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3861-262-CM25</t>
+          <t>3495-43-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.191.400-3</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>SEIDOR TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.449.580-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1594.6</v>
+        <v>14994</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3151-662-CM25</t>
+          <t>3708-258-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>18763.96</v>
+        <v>17802.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1426099-232-CM25</t>
+          <t>2387-226-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>9282</v>
+        <v>8779.76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3200-625-CM25</t>
+          <t>3705-173-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5071.46</v>
+        <v>12333.06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3887-602-CM25</t>
+          <t>4112-84-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>46156.53</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3201-450-CM25</t>
+          <t>3477-256-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SEIDOR TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.449.580-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3538.23</v>
+        <v>49180.32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3697-180-CM26</t>
+          <t>3212-99-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7096.21</v>
+        <v>846.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3486-114-CM26</t>
+          <t>5060-272-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.190.400-8</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>13744.5</v>
+        <v>1192.65</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3485-246-CM26</t>
+          <t>2387-300-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.190.400-8</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>13744.5</v>
+        <v>6404.01</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3495-61-CM26</t>
+          <t>3485-314-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.190.400-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SEIDOR TECHNOLOGIES S.A.</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.449.580-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>22184.58</v>
+        <v>12495</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>722-27-CM26</t>
+          <t>3486-355-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>69.190.400-8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>30742.22</v>
+        <v>12495</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4284-148-CM26</t>
+          <t>4406-448-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>69.180.800-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>48786.43</v>
+        <v>2115.11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2548-229-CM26</t>
+          <t>2548-526-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>9721.82</v>
+        <v>9094.959999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3708-146-CM26</t>
+          <t>514847-1118-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>32092.52</v>
+        <v>19530.28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3517-60-CM26</t>
+          <t>514848-776-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5588.26</v>
+        <v>16867.06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4322-265-CM26</t>
+          <t>4179-1620-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4015.54</v>
+        <v>62141.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4179-622-CM26</t>
+          <t>3502-511-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6424.57</v>
+        <v>12920.35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4322-332-CM26</t>
+          <t>4177-83-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>845.28</v>
+        <v>9294.07</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5586-2119-CM26</t>
+          <t>4170-213-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>62229.5</v>
+        <v>40763.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3921-323-CM26</t>
+          <t>4322-355-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>22175.65</v>
+        <v>7830.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3517-103-CM26</t>
+          <t>1057780-58-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,7 +2155,2394 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
+        <v>36168.31</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1175-2167-CM25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>61.607.400-8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>115406.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4177-111-CM25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.190.200-5</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Galvarino</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>2960.98</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2389-540-CM25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>69.191.600-6</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCON</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>3019.27</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3705-413-CM25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>69.180.300-7</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>15393.84</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4513-137-CM25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.180.400-3</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RENAICO</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>10364.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>5586-2981-CM25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>87.912.900-1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>68130.25999999999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2389-633-CM25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.191.600-6</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCON</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>887.74</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2389-710-CM25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.191.600-6</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCON</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>2537.56</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1028897-1614-CM25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>65.154.272-3</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>28141.83</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3836-935-CM25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.191.400-3</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOLTEN</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>8770.299999999999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3861-262-CM25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>69.191.400-3</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOLTEN</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>1594.6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3151-662-CM25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.191.100-4</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>18763.96</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1426099-232-CM25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Site Chile Sociedad Anónima</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>96.988.790-8</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>9282</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3200-625-CM25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.191.100-4</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>5071.46</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3887-602-CM25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>69.191.500-K</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>46156.53</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>3201-450-CM25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>69.191.100-4</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>3538.23</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3697-180-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>69.180.900-5</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>7096.21</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3485-246-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.190.400-8</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>13744.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3486-114-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.190.400-8</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>13744.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3495-61-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.190.800-3</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>SEIDOR TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.449.580-2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>22184.58</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>722-27-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>72.201.100-7</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>30742.22</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4284-148-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>69.191.000-8</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>48786.43</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3708-146-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>69.191.300-7</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>NETSUS SPA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>32092.52</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2548-229-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>9721.82</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3517-60-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.180.700-2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>CLOUDLATAM SPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>5588.26</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4322-265-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.190.300-1</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>4015.54</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4179-622-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>69.190.100-9</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>6424.57</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>4322-332-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.190.300-1</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>845.28</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>5586-2119-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>87.912.900-1</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>62229.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>3921-323-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>69.191.500-K</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>22175.65</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>3517-103-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>69.180.700-2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>CLOUDLATAM SPA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
         <v>1774.05</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>3705-389-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>69.180.300-7</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>16924.06</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>4177-92-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.190.200-5</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Galvarino</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>CLOUDLATAM SPA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>8769.74</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1078177-724-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>60.505.522-2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>2113.08</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>4323-198-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>69.190.300-1</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>1056.54</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>4170-239-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>69.190.200-5</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Galvarino</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>CLOUDLATAM SPA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>30771.02</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>5066-202-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>69.191.300-7</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Netsus SpA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>17475.15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1175-708-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>61.607.400-8</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>132839.7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3428-231-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>61.948.900-4</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>1690.47</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/araucania.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3141,7 +3141,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3697-180-CM26</t>
+          <t>3153-41-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>7096.21</v>
+        <v>12832.96</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3485-246-CM26</t>
+          <t>3697-180-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3212,27 +3212,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.190.400-8</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3257,13 +3257,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>13744.5</v>
+        <v>7096.21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3486-114-CM26</t>
+          <t>3485-246-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3324,7 +3324,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3495-61-CM26</t>
+          <t>3486-114-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.190.400-8</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SEIDOR TECHNOLOGIES S.A.</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.449.580-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3379,13 +3379,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>22184.58</v>
+        <v>13744.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>722-27-CM26</t>
+          <t>3495-61-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3400,22 +3400,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SEIDOR TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.449.580-2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>30742.22</v>
+        <v>22184.58</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4284-148-CM26</t>
+          <t>722-27-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3456,12 +3456,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>48786.43</v>
+        <v>30742.22</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3708-146-CM26</t>
+          <t>4284-148-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>32092.52</v>
+        <v>48786.43</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2548-229-CM26</t>
+          <t>3708-146-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3588,17 +3588,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>9721.82</v>
+        <v>32092.52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3517-60-CM26</t>
+          <t>2548-229-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5588.26</v>
+        <v>9721.82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4322-265-CM26</t>
+          <t>3517-60-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4015.54</v>
+        <v>5588.26</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4179-622-CM26</t>
+          <t>4322-265-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3761,27 +3761,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>6424.57</v>
+        <v>4015.54</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4322-332-CM26</t>
+          <t>4179-622-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3827,22 +3827,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>845.28</v>
+        <v>6424.57</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5586-2119-CM26</t>
+          <t>4322-332-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>62229.5</v>
+        <v>845.28</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3921-323-CM26</t>
+          <t>5586-2119-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3989,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>22175.65</v>
+        <v>62229.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3517-103-CM26</t>
+          <t>3921-323-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1774.05</v>
+        <v>22175.65</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3705-389-CM26</t>
+          <t>1417902-21-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4066,27 +4066,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>65.211.127-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>ASOCIACION DE MUNICIPALIDADES DE LA ZONA METROPOLITANA DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>16924.06</v>
+        <v>2165.01</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4177-92-CM26</t>
+          <t>3517-103-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>8769.74</v>
+        <v>1774.05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1078177-724-CM26</t>
+          <t>3705-389-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4233,13 +4233,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2113.08</v>
+        <v>16924.06</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4323-198-CM26</t>
+          <t>4177-92-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4254,22 +4254,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4294,13 +4294,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1056.54</v>
+        <v>8769.74</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4170-239-CM26</t>
+          <t>1078177-724-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4315,22 +4315,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>30771.02</v>
+        <v>2113.08</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5066-202-CM26</t>
+          <t>4323-198-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4376,22 +4376,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>17475.15</v>
+        <v>1056.54</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1175-708-CM26</t>
+          <t>4170-239-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4437,22 +4437,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4462,32 +4462,28 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>132839.7</v>
+        <v>30771.02</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3428-231-CM26</t>
+          <t>5066-202-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4502,22 +4498,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.948.900-4</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4527,12 +4523,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4542,7 +4538,259 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
+        <v>17475.15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1175-708-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>61.607.400-8</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>132839.7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3428-231-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.948.900-4</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
         <v>1690.47</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2389-523-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>69.191.600-6</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCON</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>5111.76</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>765-205-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>183483.72</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/araucania.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/araucania.xlsx
@@ -562,7 +562,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>76.449.580-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>76.449.580-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1468,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1655,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1720,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1785,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1850,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1915,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1980,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2045,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2110,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2175,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2240,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2370,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2435,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2500,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2565,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2630,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2695,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2760,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2825,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2890,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2955,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3020,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3146,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3211,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3276,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3341,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3406,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3593,11 @@
           <t>76.449.580-2</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3658,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3723,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3788,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3853,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3918,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3983,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4048,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4113,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4178,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4243,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4308,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4373,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4438,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4503,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4568,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4633,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4698,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4763,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4657,7 +4893,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4718,7 +4958,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/araucania.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3740,7 +3740,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3708-146-CM26</t>
+          <t>2548-229-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3760,17 +3760,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3799,13 +3799,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>32092.52</v>
+        <v>9721.82</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2548-229-CM26</t>
+          <t>3708-146-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3825,17 +3825,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>9721.82</v>
+        <v>32092.52</v>
       </c>
     </row>
     <row r="54">
@@ -5035,6 +5035,71 @@
       </c>
       <c r="M71" s="2" t="n">
         <v>183483.72</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2736-381-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>69.180.100-4</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>72311.89999999999</v>
       </c>
     </row>
   </sheetData>
